--- a/data/trans_orig/P6714-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2012</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34269</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61919</t>
+          <t>60447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33196</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51574</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>51565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72107</t>
+          <t>73108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98501</t>
+          <t>98833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>27076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84799</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>27562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88867</t>
+          <t>86814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127923</t>
+          <t>127666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63643</t>
+          <t>62940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96530</t>
+          <t>93733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>56918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83824</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125285</t>
+          <t>126468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168453</t>
+          <t>168979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188288</t>
+          <t>189209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227753</t>
+          <t>228395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128574</t>
+          <t>127006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161596</t>
+          <t>160202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324691</t>
+          <t>327284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380522</t>
+          <t>381320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51336</t>
+          <t>50928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81605</t>
+          <t>80063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>43897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>69802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103033</t>
+          <t>101026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145213</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85347</t>
+          <t>83876</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>119589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87473</t>
+          <t>89058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>153774</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197354</t>
+          <t>198795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215989</t>
+          <t>216065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258502</t>
+          <t>256245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124053</t>
+          <t>123479</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157509</t>
+          <t>156793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349463</t>
+          <t>347925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402112</t>
+          <t>401092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25763</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48878</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>57586</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93833</t>
+          <t>92924</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67798</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101755</t>
+          <t>102417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68070</t>
+          <t>69003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117442</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160250</t>
+          <t>160381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>217043</t>
+          <t>216321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255157</t>
+          <t>256887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104075</t>
+          <t>104759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138684</t>
+          <t>137460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332455</t>
+          <t>330640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384813</t>
+          <t>383855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,62 +3494,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5715</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>27052</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47210</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>41516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68389</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>112527</t>
+          <t>112336</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51151</t>
+          <t>51600</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>128081</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>158007</t>
+          <t>157439</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4367,97 +4367,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>67962</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>70117</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>170009</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>223968</t>
+          <t>221423</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>133635</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>181280</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>315519</t>
+          <t>314423</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>388836</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>289762</t>
+          <t>291319</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>356002</t>
+          <t>359715</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>211470</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>268045</t>
+          <t>267521</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>523105</t>
+          <t>520028</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>608341</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>786794</t>
+          <t>788887</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>865281</t>
+          <t>865000</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>457325</t>
+          <t>460768</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>523812</t>
+          <t>524402</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1265877</t>
+          <t>1268668</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1372103</t>
+          <t>1371607</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2016</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32151</t>
+          <t>32384</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>55707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62549</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41522</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47459</t>
+          <t>47341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>72366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60664</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92076</t>
+          <t>91393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68937</t>
+          <t>69203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>112660</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151019</t>
+          <t>153082</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75492</t>
+          <t>76850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>111233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>63762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92043</t>
+          <t>92067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192337</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121741</t>
+          <t>120841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158364</t>
+          <t>156987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96347</t>
+          <t>94290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127960</t>
+          <t>128322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226974</t>
+          <t>229664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274285</t>
+          <t>276081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26418</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>112273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67087</t>
+          <t>68283</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>125609</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171750</t>
+          <t>172115</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100972</t>
+          <t>99855</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139575</t>
+          <t>138999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>72408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104261</t>
+          <t>102535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182776</t>
+          <t>184219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232883</t>
+          <t>232868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>194505</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237133</t>
+          <t>237775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135049</t>
+          <t>136321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172249</t>
+          <t>170677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>340443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397747</t>
+          <t>394181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41803</t>
+          <t>41918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84813</t>
+          <t>83910</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26152</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48370</t>
+          <t>49993</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85390</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85546</t>
+          <t>85268</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119762</t>
+          <t>120399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56219</t>
+          <t>56424</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>86324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148764</t>
+          <t>152924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195904</t>
+          <t>197843</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159006</t>
+          <t>160859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197993</t>
+          <t>198555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92509</t>
+          <t>92008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123218</t>
+          <t>123217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260809</t>
+          <t>258895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>313911</t>
+          <t>311392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26493</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>59701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51390</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>54387</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82759</t>
+          <t>84597</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67063</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93429</t>
+          <t>92054</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>109978</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>148774</t>
+          <t>146608</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10093,62 +10093,62 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>52696</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50873</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>58090</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>97659</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>59474</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>91511</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>127092</t>
+          <t>125572</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>175290</t>
+          <t>172949</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>255462</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>318984</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>162240</t>
+          <t>161096</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>209433</t>
+          <t>210266</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>434669</t>
+          <t>430047</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>508551</t>
+          <t>509790</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>346522</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>417308</t>
+          <t>410788</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>265089</t>
+          <t>267257</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>324239</t>
+          <t>327275</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>622867</t>
+          <t>623586</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>713638</t>
+          <t>715936</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>605890</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>680039</t>
+          <t>683259</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>429776</t>
+          <t>424681</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>492566</t>
+          <t>489448</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1053904</t>
+          <t>1048893</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1152704</t>
+          <t>1155843</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6714-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60447</t>
+          <t>61077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51565</t>
+          <t>51657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73108</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>99467</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>28371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54242</t>
+          <t>54456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>84682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86814</t>
+          <t>88217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127666</t>
+          <t>127216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62940</t>
+          <t>63845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>94576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84367</t>
+          <t>83474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>127139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168979</t>
+          <t>169087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189209</t>
+          <t>187706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228395</t>
+          <t>227188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127006</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160202</t>
+          <t>161378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327284</t>
+          <t>325551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381320</t>
+          <t>381247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80063</t>
+          <t>80330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43897</t>
+          <t>45082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69802</t>
+          <t>71812</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101026</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141743</t>
+          <t>141801</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83876</t>
+          <t>82149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119589</t>
+          <t>118955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153774</t>
+          <t>153833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198795</t>
+          <t>197810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216065</t>
+          <t>217743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256245</t>
+          <t>257716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123479</t>
+          <t>123576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156793</t>
+          <t>157844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347925</t>
+          <t>351470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>401092</t>
+          <t>404799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27042</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>49523</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>50864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57586</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92924</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>66502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102417</t>
+          <t>103087</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69003</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115898</t>
+          <t>116288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160381</t>
+          <t>162341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>216321</t>
+          <t>214142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>256887</t>
+          <t>256055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104759</t>
+          <t>104476</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>137338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330640</t>
+          <t>329131</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383855</t>
+          <t>382571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,63%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>33704</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27052</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>48302</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41516</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68341</t>
+          <t>67857</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>112336</t>
+          <t>112761</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>34257</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>51581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>128081</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>157439</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,82 +5520,82 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>10488</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>27858</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>40287</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>30285</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>55743</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>10896</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>28388</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>40287</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>55319</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>168757</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>221423</t>
+          <t>224994</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>182021</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>314423</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>388836</t>
+          <t>386894</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>291319</t>
+          <t>288603</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>359715</t>
+          <t>357218</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>213748</t>
+          <t>212703</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>267521</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>520028</t>
+          <t>521384</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>603596</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>788887</t>
+          <t>789635</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>865000</t>
+          <t>867498</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>460768</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>524402</t>
+          <t>522657</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1268668</t>
+          <t>1272053</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1371607</t>
+          <t>1370481</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31397</t>
+          <t>31426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32384</t>
+          <t>33845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55707</t>
+          <t>56606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37969</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63787</t>
+          <t>64966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35899</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47341</t>
+          <t>46873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72366</t>
+          <t>70643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>62965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>93003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69203</t>
+          <t>68706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112660</t>
+          <t>111578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153082</t>
+          <t>151752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76850</t>
+          <t>77176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111233</t>
+          <t>108964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>64138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92067</t>
+          <t>92492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146862</t>
+          <t>148527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192578</t>
+          <t>190389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120841</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156987</t>
+          <t>156759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>94458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128322</t>
+          <t>127149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229664</t>
+          <t>229247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276081</t>
+          <t>276350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25894</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>52273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76529</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112273</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68283</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>123998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>172115</t>
+          <t>171229</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99855</t>
+          <t>100193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138999</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72408</t>
+          <t>72439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>103222</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184219</t>
+          <t>183905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232868</t>
+          <t>235039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194505</t>
+          <t>193997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237775</t>
+          <t>240625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136321</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170677</t>
+          <t>169314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340443</t>
+          <t>340117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394181</t>
+          <t>394233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41918</t>
+          <t>44757</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>53554</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83910</t>
+          <t>84578</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49993</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85872</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124043</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85268</t>
+          <t>85259</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120399</t>
+          <t>120678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86324</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152924</t>
+          <t>150792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197843</t>
+          <t>195868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160859</t>
+          <t>161473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198555</t>
+          <t>200074</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92008</t>
+          <t>91306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123217</t>
+          <t>122936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>258895</t>
+          <t>261956</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>313763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18952</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>33395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>58978</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51987</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,47 +9504,47 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>27647</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>18988</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>38012</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>17,93%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>27647</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>19063</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>38748</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>53449</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84597</t>
+          <t>82898</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>66503</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92054</t>
+          <t>92659</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>60038</t>
+          <t>60004</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>109978</t>
+          <t>112651</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>146608</t>
+          <t>147972</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>51436</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>85397</t>
+          <t>85485</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>58090</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>125572</t>
+          <t>127148</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>175728</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>257661</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>317637</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>161096</t>
+          <t>160892</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>210266</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>430047</t>
+          <t>430212</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>509790</t>
+          <t>514825</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>410788</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>267257</t>
+          <t>264339</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>327275</t>
+          <t>323364</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>623586</t>
+          <t>624891</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>715936</t>
+          <t>712366</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>605890</t>
+          <t>607478</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>683259</t>
+          <t>686802</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>424681</t>
+          <t>425403</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>489448</t>
+          <t>490477</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1048893</t>
+          <t>1050849</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1155843</t>
+          <t>1150343</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
